--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2022_los_lagos.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2022_los_lagos.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:39</t>
+    <t xml:space="preserve">2026-09-24 01:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -739,7 +739,7 @@
         <v>-0.14</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.18</v>
@@ -759,10 +759,10 @@
         <v>30</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>-0.42</v>
@@ -782,10 +782,10 @@
         <v>30</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0.35</v>
@@ -799,19 +799,19 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="14">
@@ -845,19 +845,19 @@
         <v>25</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.13</v>
+        <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.09</v>
+        <v>-0.14</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>322</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.22</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="16">
@@ -868,7 +868,7 @@
         <v>25</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>30</v>
@@ -880,7 +880,7 @@
         <v>322</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="17">
@@ -891,19 +891,19 @@
         <v>25</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.21</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.19</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>322</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="18">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2022_los_lagos.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2022_los_lagos.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:29</t>
+    <t xml:space="preserve">2026-10-01 23:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2022_los_lagos.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2022_los_lagos.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:14</t>
+    <t xml:space="preserve">2026-10-05 19:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
